--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,6 +910,327 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113439181</v>
+      </c>
+      <c r="B4" t="n">
+        <v>77857</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjärnmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>760313</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7171032</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113439134</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78671</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjärnmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>760279</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7171021</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113439125</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78697</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjärnmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>760279</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7171019</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>113439181</v>
       </c>
       <c r="B4" t="n">
-        <v>77857</v>
+        <v>77873</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439134</v>
+        <v>113439125</v>
       </c>
       <c r="B5" t="n">
-        <v>78671</v>
+        <v>78713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
         <v>760279</v>
       </c>
       <c r="R5" t="n">
-        <v>7171021</v>
+        <v>7171019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439125</v>
+        <v>113439134</v>
       </c>
       <c r="B6" t="n">
-        <v>78697</v>
+        <v>78687</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
         <v>760279</v>
       </c>
       <c r="R6" t="n">
-        <v>7171019</v>
+        <v>7171021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439181</v>
+        <v>113439125</v>
       </c>
       <c r="B4" t="n">
-        <v>77873</v>
+        <v>78713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R4" t="n">
-        <v>7171032</v>
+        <v>7171019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439125</v>
+        <v>113439134</v>
       </c>
       <c r="B5" t="n">
-        <v>78713</v>
+        <v>78687</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
         <v>760279</v>
       </c>
       <c r="R5" t="n">
-        <v>7171019</v>
+        <v>7171021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439134</v>
+        <v>113439181</v>
       </c>
       <c r="B6" t="n">
-        <v>78687</v>
+        <v>77873</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R6" t="n">
-        <v>7171021</v>
+        <v>7171032</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439125</v>
+        <v>113439181</v>
       </c>
       <c r="B4" t="n">
-        <v>78713</v>
+        <v>77885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R4" t="n">
-        <v>7171019</v>
+        <v>7171032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439134</v>
+        <v>113439125</v>
       </c>
       <c r="B5" t="n">
-        <v>78687</v>
+        <v>78725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
         <v>760279</v>
       </c>
       <c r="R5" t="n">
-        <v>7171021</v>
+        <v>7171019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439181</v>
+        <v>113439134</v>
       </c>
       <c r="B6" t="n">
-        <v>77873</v>
+        <v>78699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R6" t="n">
-        <v>7171032</v>
+        <v>7171021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439181</v>
+        <v>113439134</v>
       </c>
       <c r="B4" t="n">
-        <v>77885</v>
+        <v>78699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R4" t="n">
-        <v>7171032</v>
+        <v>7171021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439125</v>
+        <v>113439181</v>
       </c>
       <c r="B5" t="n">
-        <v>78725</v>
+        <v>77885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R5" t="n">
-        <v>7171019</v>
+        <v>7171032</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439134</v>
+        <v>113439125</v>
       </c>
       <c r="B6" t="n">
-        <v>78699</v>
+        <v>78725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
         <v>760279</v>
       </c>
       <c r="R6" t="n">
-        <v>7171021</v>
+        <v>7171019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439134</v>
+        <v>113439125</v>
       </c>
       <c r="B4" t="n">
-        <v>78699</v>
+        <v>78747</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,7 +955,7 @@
         <v>760279</v>
       </c>
       <c r="R4" t="n">
-        <v>7171021</v>
+        <v>7171019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439181</v>
+        <v>113439134</v>
       </c>
       <c r="B5" t="n">
-        <v>77885</v>
+        <v>78721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R5" t="n">
-        <v>7171032</v>
+        <v>7171021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439125</v>
+        <v>113439181</v>
       </c>
       <c r="B6" t="n">
-        <v>78725</v>
+        <v>77907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R6" t="n">
-        <v>7171019</v>
+        <v>7171032</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439125</v>
+        <v>113439181</v>
       </c>
       <c r="B4" t="n">
-        <v>78747</v>
+        <v>77910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R4" t="n">
-        <v>7171019</v>
+        <v>7171032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439134</v>
+        <v>113439125</v>
       </c>
       <c r="B5" t="n">
-        <v>78721</v>
+        <v>78751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
         <v>760279</v>
       </c>
       <c r="R5" t="n">
-        <v>7171021</v>
+        <v>7171019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439181</v>
+        <v>113439134</v>
       </c>
       <c r="B6" t="n">
-        <v>77907</v>
+        <v>78725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R6" t="n">
-        <v>7171032</v>
+        <v>7171021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>113439181</v>
       </c>
       <c r="B4" t="n">
-        <v>77910</v>
+        <v>77916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439125</v>
+        <v>113439134</v>
       </c>
       <c r="B5" t="n">
-        <v>78751</v>
+        <v>78731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
         <v>760279</v>
       </c>
       <c r="R5" t="n">
-        <v>7171019</v>
+        <v>7171021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439134</v>
+        <v>113439125</v>
       </c>
       <c r="B6" t="n">
-        <v>78725</v>
+        <v>78757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
         <v>760279</v>
       </c>
       <c r="R6" t="n">
-        <v>7171021</v>
+        <v>7171019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439181</v>
+        <v>113439125</v>
       </c>
       <c r="B4" t="n">
-        <v>77916</v>
+        <v>78764</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R4" t="n">
-        <v>7171032</v>
+        <v>7171019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439134</v>
+        <v>113439181</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>77923</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R5" t="n">
-        <v>7171021</v>
+        <v>7171032</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439125</v>
+        <v>113439134</v>
       </c>
       <c r="B6" t="n">
-        <v>78757</v>
+        <v>78738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
         <v>760279</v>
       </c>
       <c r="R6" t="n">
-        <v>7171019</v>
+        <v>7171021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439125</v>
+        <v>113439181</v>
       </c>
       <c r="B4" t="n">
-        <v>78764</v>
+        <v>77925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R4" t="n">
-        <v>7171019</v>
+        <v>7171032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439181</v>
+        <v>113439134</v>
       </c>
       <c r="B5" t="n">
-        <v>77923</v>
+        <v>78740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R5" t="n">
-        <v>7171032</v>
+        <v>7171021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439134</v>
+        <v>113439125</v>
       </c>
       <c r="B6" t="n">
-        <v>78738</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
         <v>760279</v>
       </c>
       <c r="R6" t="n">
-        <v>7171021</v>
+        <v>7171019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439181</v>
+        <v>113439134</v>
       </c>
       <c r="B4" t="n">
-        <v>77925</v>
+        <v>78768</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R4" t="n">
-        <v>7171032</v>
+        <v>7171021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439134</v>
+        <v>113439181</v>
       </c>
       <c r="B5" t="n">
-        <v>78740</v>
+        <v>77953</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R5" t="n">
-        <v>7171021</v>
+        <v>7171032</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1129,7 @@
         <v>113439125</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78794</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439134</v>
+        <v>113439181</v>
       </c>
       <c r="B4" t="n">
-        <v>78768</v>
+        <v>77953</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R4" t="n">
-        <v>7171021</v>
+        <v>7171032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439181</v>
+        <v>113439125</v>
       </c>
       <c r="B5" t="n">
-        <v>77953</v>
+        <v>78794</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R5" t="n">
-        <v>7171032</v>
+        <v>7171019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113439125</v>
+        <v>113439134</v>
       </c>
       <c r="B6" t="n">
-        <v>78794</v>
+        <v>78768</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
         <v>760279</v>
       </c>
       <c r="R6" t="n">
-        <v>7171019</v>
+        <v>7171021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113439181</v>
+        <v>113439125</v>
       </c>
       <c r="B4" t="n">
-        <v>77953</v>
+        <v>78794</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760313</v>
+        <v>760279</v>
       </c>
       <c r="R4" t="n">
-        <v>7171032</v>
+        <v>7171019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113439125</v>
+        <v>113439181</v>
       </c>
       <c r="B5" t="n">
-        <v>78794</v>
+        <v>77953</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760279</v>
+        <v>760313</v>
       </c>
       <c r="R5" t="n">
-        <v>7171019</v>
+        <v>7171032</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 34250-2021 artfynd.xlsx
+++ b/artfynd/A 34250-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
